--- a/output/pdf_financials_xlsx/ENBI.X.xlsx
+++ b/output/pdf_financials_xlsx/ENBI.X.xlsx
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="17">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="21">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="24">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6.00002</v>
+        <v>-6.00002</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-7.948075</v>
+        <v>7.948075</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-16.2006</v>
+        <v>16.2006</v>
       </c>
     </row>
     <row r="27">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="28">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8.522828000000001</v>
+        <v>-8.518637999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="30">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>4493.337621324673</v>
+        <v>-4491.128602835347</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>119.8455595370781</v>
+        <v>-119.8455595370781</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4492.23311208001</v>
+        <v>-4492.23311208001</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>119.8455595370781</v>
+        <v>-119.8455595370781</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -2215,16 +2215,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.87223</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.663366</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.961866</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.591013</v>
       </c>
     </row>
     <row r="93">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.300001</v>
@@ -3394,7 +3394,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3570,7 +3574,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3642,7 +3650,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>2.87223</v>
       </c>
@@ -5004,10 +5016,10 @@
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.324012</v>
+        <v>-0.324012</v>
       </c>
     </row>
     <row r="56">
@@ -5445,10 +5457,10 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.317923</v>
+        <v>-0.317923</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5994,10 +6006,10 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>8.520733</v>
+        <v>-8.520733</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.300001</v>
+        <v>-0.300001</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ENBI.X.xlsx
+++ b/output/pdf_financials_xlsx/ENBI.X.xlsx
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007560000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007323</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015107</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010272</v>
       </c>
     </row>
     <row r="13">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.520733</v>
+        <v>-8.519977000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.300001</v>
+        <v>-0.292678</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.317923</v>
+        <v>-0.302816</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.324012</v>
+        <v>-0.31374</v>
       </c>
     </row>
     <row r="28">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.518637999999999</v>
+        <v>-8.517882</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.300001</v>
+        <v>-0.292678</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.317923</v>
+        <v>-0.302816</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.324012</v>
+        <v>-0.31374</v>
       </c>
     </row>
     <row r="30">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4491.128602835347</v>
+        <v>-4490.730030525578</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-119.8455595370781</v>
+        <v>-116.9201391801792</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENBI.X.xlsx
+++ b/output/pdf_financials_xlsx/ENBI.X.xlsx
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-8.520733</v>
+        <v>-2.061475</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.300001</v>
@@ -4426,7 +4426,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>-2.061475</v>
       </c>
